--- a/smartcards_Testdecks.xlsx
+++ b/smartcards_Testdecks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Dropbox\07 Entwicklungen\02_SmartCards\04_SmartCards_Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4206631-BED8-47B4-A282-3EA7981743D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7900FE2-A8E3-4F61-9C53-EC0580FEEA3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Anleitung" sheetId="1" r:id="rId1"/>
@@ -422,9 +422,6 @@
 Insekten haben nur 6 Beine.</t>
   </si>
   <si>
-    <t>https://media.istockphoto.com/photos/top-view-of-a-redknee-tarantula-isolated-against-white-background-picture-id172826272?k=20&amp;m=172826272&amp;s=170667a&amp;w=0&amp;h=C_QqMS1_QrxnND6k2JtNo7TxA3DDNd4qqDP1eVd0J50=</t>
-  </si>
-  <si>
     <t>Es ist die einzige nennenswerte Erhebung innerhalb der historischen Münchner Altstadt.</t>
   </si>
   <si>
@@ -570,13 +567,16 @@
 Die Kugel ist noch heute oben in der Chorwand eingemauert zu sehen.</t>
   </si>
   <si>
-    <t>https://th.bing.com/th/id/R.7c4a49fccb47ebb213de04ebf468e276?rik=vrL4JMx9EN932w&amp;pid=ImgRaw&amp;r=0</t>
-  </si>
-  <si>
-    <t>https://tse1.mm.bing.net/th/id/OIP.v_DSH9eI_wuhpa0l0Ior_QHaJ4?r=0&amp;rs=1&amp;pid=ImgDetMain&amp;o=7&amp;rm=3</t>
-  </si>
-  <si>
     <t>https://alterpeter.de/wp-content/uploads/2020/05/01_Jubil%C3%A4umsglocke_2457-1365x2048.jpg</t>
+  </si>
+  <si>
+    <t>https://alterpeter.de/wp-content/uploads/2020/05/alter_peter_uhr_3-768x1152.jpg</t>
+  </si>
+  <si>
+    <t>https://alterpeter.de/wp-content/uploads/2021/10/03_Das_Treppenhaus_im_Alten_Peter_bei_Nacht.jpg</t>
+  </si>
+  <si>
+    <t>https://www.tropic-shop.de/images/content/Bilder_Artikelbeschreibungen/Vogelspinnen/Vogespinnen%20auf%20Sandigem%20Bodengrund.jpg</t>
   </si>
 </sst>
 </file>
@@ -1419,7 +1419,7 @@
         <v>130</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>131</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -1448,9 +1448,6 @@
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="E4" r:id="rId1" xr:uid="{7B978EF4-09CA-4293-B338-F764A0847B4F}"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1708,12 +1705,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -1735,31 +1732,31 @@
     </row>
     <row r="4" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E4" s="12"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E5" s="11" t="s">
         <v>178</v>
@@ -1767,31 +1764,31 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E6" s="12"/>
     </row>
     <row r="7" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E7" s="11" t="s">
         <v>179</v>
@@ -1799,161 +1796,159 @@
     </row>
     <row r="8" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="D8" s="15" t="s">
         <v>172</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>173</v>
       </c>
       <c r="E8" s="12"/>
     </row>
     <row r="9" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E9" s="12"/>
     </row>
     <row r="10" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E10" s="12"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E12" s="12"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E13" s="12"/>
     </row>
     <row r="14" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E14" s="12"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E15" s="12"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E16" s="12"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E17" s="12"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E5" r:id="rId1" xr:uid="{97BC2476-1FBF-4BEC-8A05-B80E8D8CE111}"/>
-    <hyperlink ref="E7" r:id="rId2" xr:uid="{A1C25D90-B960-475A-B29B-224884370A80}"/>
-    <hyperlink ref="E11" r:id="rId3" xr:uid="{2F91173F-456C-4EC5-81E0-8FB1C4F0BD5B}"/>
+    <hyperlink ref="E11" r:id="rId1" xr:uid="{2F91173F-456C-4EC5-81E0-8FB1C4F0BD5B}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
